--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859619</v>
+        <v>124859561</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542105</v>
+        <v>542076</v>
       </c>
       <c r="R2" t="n">
-        <v>6404972</v>
+        <v>6405042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859624</v>
+        <v>124859587</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542028</v>
+        <v>542024</v>
       </c>
       <c r="R3" t="n">
-        <v>6404993</v>
+        <v>6405028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859606</v>
+        <v>124859644</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542297</v>
+        <v>542174</v>
       </c>
       <c r="R4" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859587</v>
+        <v>124859578</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542024</v>
+        <v>542132</v>
       </c>
       <c r="R5" t="n">
-        <v>6405028</v>
+        <v>6404971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859561</v>
+        <v>124859606</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,7 +1169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1187,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542076</v>
+        <v>542297</v>
       </c>
       <c r="R6" t="n">
-        <v>6405042</v>
+        <v>6405013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859578</v>
+        <v>124859619</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1284,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542132</v>
+        <v>542105</v>
       </c>
       <c r="R7" t="n">
-        <v>6404971</v>
+        <v>6404972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859644</v>
+        <v>124859615</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1376,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542174</v>
+        <v>542208</v>
       </c>
       <c r="R8" t="n">
-        <v>6405042</v>
+        <v>6404985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,6 +1460,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859615</v>
+        <v>124859624</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542208</v>
+        <v>542028</v>
       </c>
       <c r="R9" t="n">
-        <v>6404985</v>
+        <v>6404993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859561</v>
+        <v>124859624</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542076</v>
+        <v>542028</v>
       </c>
       <c r="R2" t="n">
-        <v>6405042</v>
+        <v>6404993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859587</v>
+        <v>124859615</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542024</v>
+        <v>542208</v>
       </c>
       <c r="R3" t="n">
-        <v>6405028</v>
+        <v>6404985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859644</v>
+        <v>124859578</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542174</v>
+        <v>542132</v>
       </c>
       <c r="R4" t="n">
-        <v>6405042</v>
+        <v>6404971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,6 +1001,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859578</v>
+        <v>124859606</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1054,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1071,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542132</v>
+        <v>542297</v>
       </c>
       <c r="R5" t="n">
-        <v>6404971</v>
+        <v>6405013</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859606</v>
+        <v>124859587</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1169,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542297</v>
+        <v>542024</v>
       </c>
       <c r="R6" t="n">
-        <v>6405013</v>
+        <v>6405028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859619</v>
+        <v>124859561</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1284,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542105</v>
+        <v>542076</v>
       </c>
       <c r="R7" t="n">
-        <v>6404972</v>
+        <v>6405042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859615</v>
+        <v>124859619</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1399,7 +1400,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542208</v>
+        <v>542105</v>
       </c>
       <c r="R8" t="n">
-        <v>6404985</v>
+        <v>6404972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859624</v>
+        <v>124859644</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,39 +1492,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542028</v>
+        <v>542174</v>
       </c>
       <c r="R9" t="n">
-        <v>6404993</v>
+        <v>6405042</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1576,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859624</v>
+        <v>124859606</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542028</v>
+        <v>542297</v>
       </c>
       <c r="R2" t="n">
-        <v>6404993</v>
+        <v>6405013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859615</v>
+        <v>124859624</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542208</v>
+        <v>542028</v>
       </c>
       <c r="R3" t="n">
-        <v>6404985</v>
+        <v>6404993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859578</v>
+        <v>124859615</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542132</v>
+        <v>542208</v>
       </c>
       <c r="R4" t="n">
-        <v>6404971</v>
+        <v>6404985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859606</v>
+        <v>124859587</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542297</v>
+        <v>542024</v>
       </c>
       <c r="R5" t="n">
-        <v>6405013</v>
+        <v>6405028</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859587</v>
+        <v>124859619</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542024</v>
+        <v>542105</v>
       </c>
       <c r="R6" t="n">
-        <v>6405028</v>
+        <v>6404972</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859619</v>
+        <v>124859644</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1377,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542105</v>
+        <v>542174</v>
       </c>
       <c r="R8" t="n">
-        <v>6404972</v>
+        <v>6405042</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859644</v>
+        <v>124859578</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,39 +1491,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542174</v>
+        <v>542132</v>
       </c>
       <c r="R9" t="n">
-        <v>6405042</v>
+        <v>6404971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,6 +1575,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859606</v>
+        <v>124859619</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542297</v>
+        <v>542105</v>
       </c>
       <c r="R2" t="n">
-        <v>6405013</v>
+        <v>6404972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859624</v>
+        <v>124859587</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542028</v>
+        <v>542024</v>
       </c>
       <c r="R3" t="n">
-        <v>6404993</v>
+        <v>6405028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859615</v>
+        <v>124859624</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542208</v>
+        <v>542028</v>
       </c>
       <c r="R4" t="n">
-        <v>6404985</v>
+        <v>6404993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859587</v>
+        <v>124859615</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542024</v>
+        <v>542208</v>
       </c>
       <c r="R5" t="n">
-        <v>6405028</v>
+        <v>6404985</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859619</v>
+        <v>124859644</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,39 +1147,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542105</v>
+        <v>542174</v>
       </c>
       <c r="R6" t="n">
-        <v>6404972</v>
+        <v>6405042</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1231,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859561</v>
+        <v>124859606</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1284,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542076</v>
+        <v>542297</v>
       </c>
       <c r="R7" t="n">
-        <v>6405042</v>
+        <v>6405013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859644</v>
+        <v>124859578</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,39 +1376,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542174</v>
+        <v>542132</v>
       </c>
       <c r="R8" t="n">
-        <v>6405042</v>
+        <v>6404971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,6 +1460,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859578</v>
+        <v>124859561</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542132</v>
+        <v>542076</v>
       </c>
       <c r="R9" t="n">
-        <v>6404971</v>
+        <v>6405042</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859619</v>
+        <v>124859578</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542105</v>
+        <v>542132</v>
       </c>
       <c r="R2" t="n">
-        <v>6404972</v>
+        <v>6404971</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859587</v>
+        <v>124859619</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542024</v>
+        <v>542105</v>
       </c>
       <c r="R3" t="n">
-        <v>6405028</v>
+        <v>6404972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859624</v>
+        <v>124859587</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542028</v>
+        <v>542024</v>
       </c>
       <c r="R4" t="n">
-        <v>6404993</v>
+        <v>6405028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859644</v>
+        <v>124859561</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,39 +1147,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542174</v>
+        <v>542076</v>
       </c>
       <c r="R6" t="n">
         <v>6405042</v>
@@ -1231,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859606</v>
+        <v>124859644</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1262,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542297</v>
+        <v>542174</v>
       </c>
       <c r="R7" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859578</v>
+        <v>124859624</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542132</v>
+        <v>542028</v>
       </c>
       <c r="R8" t="n">
-        <v>6404971</v>
+        <v>6404993</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859561</v>
+        <v>124859606</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542076</v>
+        <v>542297</v>
       </c>
       <c r="R9" t="n">
-        <v>6405042</v>
+        <v>6405013</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859578</v>
+        <v>124859644</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542132</v>
+        <v>542174</v>
       </c>
       <c r="R2" t="n">
-        <v>6404971</v>
+        <v>6405042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859619</v>
+        <v>124859615</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542105</v>
+        <v>542208</v>
       </c>
       <c r="R3" t="n">
-        <v>6404972</v>
+        <v>6404985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859587</v>
+        <v>124859619</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +939,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542024</v>
+        <v>542105</v>
       </c>
       <c r="R4" t="n">
-        <v>6405028</v>
+        <v>6404972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859615</v>
+        <v>124859578</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542208</v>
+        <v>542132</v>
       </c>
       <c r="R5" t="n">
-        <v>6404985</v>
+        <v>6404971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859561</v>
+        <v>124859587</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,7 +1169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1187,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542076</v>
+        <v>542024</v>
       </c>
       <c r="R6" t="n">
-        <v>6405042</v>
+        <v>6405028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859644</v>
+        <v>124859606</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,39 +1261,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542174</v>
+        <v>542297</v>
       </c>
       <c r="R7" t="n">
-        <v>6405042</v>
+        <v>6405013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859606</v>
+        <v>124859561</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542297</v>
+        <v>542076</v>
       </c>
       <c r="R9" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859644</v>
+        <v>124859615</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542174</v>
+        <v>542208</v>
       </c>
       <c r="R2" t="n">
-        <v>6405042</v>
+        <v>6404985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859615</v>
+        <v>124859644</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542208</v>
+        <v>542174</v>
       </c>
       <c r="R3" t="n">
-        <v>6404985</v>
+        <v>6405042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859615</v>
+        <v>124859644</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542208</v>
+        <v>542174</v>
       </c>
       <c r="R2" t="n">
-        <v>6404985</v>
+        <v>6405042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859644</v>
+        <v>124859615</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542174</v>
+        <v>542208</v>
       </c>
       <c r="R3" t="n">
-        <v>6405042</v>
+        <v>6404985</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859644</v>
+        <v>124859615</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542174</v>
+        <v>542208</v>
       </c>
       <c r="R2" t="n">
-        <v>6405042</v>
+        <v>6404985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859615</v>
+        <v>124859561</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -824,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542208</v>
+        <v>542076</v>
       </c>
       <c r="R3" t="n">
-        <v>6404985</v>
+        <v>6405042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859619</v>
+        <v>124859624</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -939,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -956,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542105</v>
+        <v>542028</v>
       </c>
       <c r="R4" t="n">
-        <v>6404972</v>
+        <v>6404993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859578</v>
+        <v>124859619</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1054,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1071,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542132</v>
+        <v>542105</v>
       </c>
       <c r="R5" t="n">
-        <v>6404971</v>
+        <v>6404972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1249,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859606</v>
+        <v>124859644</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,39 +1262,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1301,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542297</v>
+        <v>542174</v>
       </c>
       <c r="R7" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859624</v>
+        <v>124859606</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542028</v>
+        <v>542297</v>
       </c>
       <c r="R8" t="n">
-        <v>6404993</v>
+        <v>6405013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859561</v>
+        <v>124859578</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542076</v>
+        <v>542132</v>
       </c>
       <c r="R9" t="n">
-        <v>6405042</v>
+        <v>6404971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859615</v>
+        <v>124859561</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542208</v>
+        <v>542076</v>
       </c>
       <c r="R2" t="n">
-        <v>6404985</v>
+        <v>6405042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859561</v>
+        <v>124859644</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542076</v>
+        <v>542174</v>
       </c>
       <c r="R3" t="n">
         <v>6405042</v>
@@ -886,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859624</v>
+        <v>124859606</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +939,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542028</v>
+        <v>542297</v>
       </c>
       <c r="R4" t="n">
-        <v>6404993</v>
+        <v>6405013</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1135,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859587</v>
+        <v>124859615</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,7 +1169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1187,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542024</v>
+        <v>542208</v>
       </c>
       <c r="R6" t="n">
-        <v>6405028</v>
+        <v>6404985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859644</v>
+        <v>124859578</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,39 +1261,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542174</v>
+        <v>542132</v>
       </c>
       <c r="R7" t="n">
-        <v>6405042</v>
+        <v>6404971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859606</v>
+        <v>124859624</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542297</v>
+        <v>542028</v>
       </c>
       <c r="R8" t="n">
-        <v>6405013</v>
+        <v>6404993</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859578</v>
+        <v>124859587</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542132</v>
+        <v>542024</v>
       </c>
       <c r="R9" t="n">
-        <v>6404971</v>
+        <v>6405028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859561</v>
+        <v>124859615</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542076</v>
+        <v>542208</v>
       </c>
       <c r="R2" t="n">
-        <v>6405042</v>
+        <v>6404985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859644</v>
+        <v>124859587</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542174</v>
+        <v>542024</v>
       </c>
       <c r="R3" t="n">
-        <v>6405042</v>
+        <v>6405028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859606</v>
+        <v>124859561</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -939,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -956,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542297</v>
+        <v>542076</v>
       </c>
       <c r="R4" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859619</v>
+        <v>124859624</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1054,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1071,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542105</v>
+        <v>542028</v>
       </c>
       <c r="R5" t="n">
-        <v>6404972</v>
+        <v>6404993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859615</v>
+        <v>124859644</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,39 +1147,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542208</v>
+        <v>542174</v>
       </c>
       <c r="R6" t="n">
-        <v>6404985</v>
+        <v>6405042</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1231,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859578</v>
+        <v>124859619</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542132</v>
+        <v>542105</v>
       </c>
       <c r="R7" t="n">
-        <v>6404971</v>
+        <v>6404972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859624</v>
+        <v>124859578</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542028</v>
+        <v>542132</v>
       </c>
       <c r="R8" t="n">
-        <v>6404993</v>
+        <v>6404971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859587</v>
+        <v>124859606</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542024</v>
+        <v>542297</v>
       </c>
       <c r="R9" t="n">
-        <v>6405028</v>
+        <v>6405013</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859615</v>
+        <v>124859619</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542208</v>
+        <v>542105</v>
       </c>
       <c r="R2" t="n">
-        <v>6404985</v>
+        <v>6404972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859587</v>
+        <v>124859606</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542024</v>
+        <v>542297</v>
       </c>
       <c r="R3" t="n">
-        <v>6405028</v>
+        <v>6405013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859561</v>
+        <v>124859624</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542076</v>
+        <v>542028</v>
       </c>
       <c r="R4" t="n">
-        <v>6405042</v>
+        <v>6404993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859624</v>
+        <v>124859578</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542028</v>
+        <v>542132</v>
       </c>
       <c r="R5" t="n">
-        <v>6404993</v>
+        <v>6404971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859644</v>
+        <v>124859587</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,39 +1147,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542174</v>
+        <v>542024</v>
       </c>
       <c r="R6" t="n">
-        <v>6405042</v>
+        <v>6405028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859619</v>
+        <v>124859561</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1284,7 +1285,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542105</v>
+        <v>542076</v>
       </c>
       <c r="R7" t="n">
-        <v>6404972</v>
+        <v>6405042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859578</v>
+        <v>124859615</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1399,7 +1400,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542132</v>
+        <v>542208</v>
       </c>
       <c r="R8" t="n">
-        <v>6404971</v>
+        <v>6404985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859606</v>
+        <v>124859644</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,39 +1492,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542297</v>
+        <v>542174</v>
       </c>
       <c r="R9" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1576,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859619</v>
+        <v>124859587</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542105</v>
+        <v>542024</v>
       </c>
       <c r="R2" t="n">
-        <v>6404972</v>
+        <v>6405028</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859606</v>
+        <v>124859644</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542297</v>
+        <v>542174</v>
       </c>
       <c r="R3" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859624</v>
+        <v>124859578</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -940,7 +939,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542028</v>
+        <v>542132</v>
       </c>
       <c r="R4" t="n">
-        <v>6404993</v>
+        <v>6404971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859578</v>
+        <v>124859624</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1055,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1072,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542132</v>
+        <v>542028</v>
       </c>
       <c r="R5" t="n">
-        <v>6404971</v>
+        <v>6404993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859587</v>
+        <v>124859561</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1170,7 +1169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1187,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542024</v>
+        <v>542076</v>
       </c>
       <c r="R6" t="n">
-        <v>6405028</v>
+        <v>6405042</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859561</v>
+        <v>124859619</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1285,7 +1284,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1302,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542076</v>
+        <v>542105</v>
       </c>
       <c r="R7" t="n">
-        <v>6405042</v>
+        <v>6404972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1480,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859644</v>
+        <v>124859606</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,39 +1491,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542174</v>
+        <v>542297</v>
       </c>
       <c r="R9" t="n">
-        <v>6405042</v>
+        <v>6405013</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,6 +1575,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859587</v>
+        <v>124859561</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542024</v>
+        <v>542076</v>
       </c>
       <c r="R2" t="n">
-        <v>6405028</v>
+        <v>6405042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859644</v>
+        <v>124859606</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542174</v>
+        <v>542297</v>
       </c>
       <c r="R3" t="n">
-        <v>6405042</v>
+        <v>6405013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,6 +886,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,7 +908,7 @@
         <v>124859578</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1019,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124859624</v>
+        <v>124859644</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>58001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,39 +1032,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542028</v>
+        <v>542174</v>
       </c>
       <c r="R5" t="n">
-        <v>6404993</v>
+        <v>6405042</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1116,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859561</v>
+        <v>124859615</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542076</v>
+        <v>542208</v>
       </c>
       <c r="R6" t="n">
-        <v>6405042</v>
+        <v>6404985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859619</v>
+        <v>124859624</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542105</v>
+        <v>542028</v>
       </c>
       <c r="R7" t="n">
-        <v>6404972</v>
+        <v>6404993</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859615</v>
+        <v>124859619</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542208</v>
+        <v>542105</v>
       </c>
       <c r="R8" t="n">
-        <v>6404985</v>
+        <v>6404972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859606</v>
+        <v>124859587</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542297</v>
+        <v>542024</v>
       </c>
       <c r="R9" t="n">
-        <v>6405013</v>
+        <v>6405028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124859561</v>
+        <v>124859619</v>
       </c>
       <c r="B2" t="n">
         <v>98269</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542076</v>
+        <v>542105</v>
       </c>
       <c r="R2" t="n">
-        <v>6405042</v>
+        <v>6404972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859606</v>
+        <v>124859561</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542297</v>
+        <v>542076</v>
       </c>
       <c r="R3" t="n">
-        <v>6405013</v>
+        <v>6405042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859578</v>
+        <v>124859615</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542132</v>
+        <v>542208</v>
       </c>
       <c r="R4" t="n">
-        <v>6404971</v>
+        <v>6404985</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124859615</v>
+        <v>124859624</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542208</v>
+        <v>542028</v>
       </c>
       <c r="R6" t="n">
-        <v>6404985</v>
+        <v>6404993</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859624</v>
+        <v>124859587</v>
       </c>
       <c r="B7" t="n">
         <v>98269</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542028</v>
+        <v>542024</v>
       </c>
       <c r="R7" t="n">
-        <v>6404993</v>
+        <v>6405028</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859619</v>
+        <v>124859578</v>
       </c>
       <c r="B8" t="n">
         <v>98269</v>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542105</v>
+        <v>542132</v>
       </c>
       <c r="R8" t="n">
-        <v>6404972</v>
+        <v>6404971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859587</v>
+        <v>124859606</v>
       </c>
       <c r="B9" t="n">
         <v>98269</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542024</v>
+        <v>542297</v>
       </c>
       <c r="R9" t="n">
-        <v>6405028</v>
+        <v>6405013</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 17978-2025 artfynd.xlsx
+++ b/artfynd/A 17978-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>98269</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>VU</t>
@@ -790,16 +785,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124859561</v>
+        <v>124859578</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>VU</t>
@@ -825,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542076</v>
+        <v>542132</v>
       </c>
       <c r="R3" t="n">
-        <v>6405042</v>
+        <v>6404971</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124859615</v>
+        <v>124859606</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542208</v>
+        <v>542297</v>
       </c>
       <c r="R4" t="n">
-        <v>6404985</v>
+        <v>6405013</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,11 +1010,6 @@
       <c r="B5" t="n">
         <v>58001</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1139,11 +1119,6 @@
       <c r="B6" t="n">
         <v>98269</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1249,16 +1224,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124859587</v>
+        <v>124859561</v>
       </c>
       <c r="B7" t="n">
         <v>98269</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1284,7 +1254,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542024</v>
+        <v>542076</v>
       </c>
       <c r="R7" t="n">
-        <v>6405028</v>
+        <v>6405042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,16 +1334,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124859578</v>
+        <v>124859587</v>
       </c>
       <c r="B8" t="n">
         <v>98269</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>VU</t>
@@ -1399,7 +1364,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1416,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542132</v>
+        <v>542024</v>
       </c>
       <c r="R8" t="n">
-        <v>6404971</v>
+        <v>6405028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,15 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124859606</v>
+        <v>124859615</v>
       </c>
       <c r="B9" t="n">
         <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542297</v>
+        <v>542208</v>
       </c>
       <c r="R9" t="n">
-        <v>6405013</v>
+        <v>6404985</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
